--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132327023</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58122</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>375642</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6279770</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>132327023</v>
       </c>
       <c r="B4" t="n">
-        <v>58122</v>
+        <v>58124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>132327023</v>
       </c>
       <c r="B4" t="n">
-        <v>58124</v>
+        <v>58125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>132327023</v>
       </c>
       <c r="B4" t="n">
-        <v>58125</v>
+        <v>58129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>92823061</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375438.7078234678</v>
+        <v>375439</v>
       </c>
       <c r="R2" t="n">
-        <v>6279745.992373742</v>
+        <v>6279746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,16 +785,11 @@
         <v>97881203</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375674.6086093738</v>
+        <v>375675</v>
       </c>
       <c r="R3" t="n">
-        <v>6279745.061380561</v>
+        <v>6279746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +896,7 @@
         <v>132327023</v>
       </c>
       <c r="B4" t="n">
-        <v>58133</v>
+        <v>58151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,6 +1002,988 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>91239073</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>375413</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6279765</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89325821</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>375655</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6279643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89893273</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>375696</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6279765</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-12-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-12-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111224367</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>375633</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6279632</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>90637603</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>375685</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6279752</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>90637601</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>375689</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6279750</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111224373</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>375371</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6279783</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119255844</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43219</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>375414</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6279874</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89893274</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>375701</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6279767</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-12-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-12-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30046-2023 artfynd.xlsx
+++ b/artfynd/A 30046-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92823061</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97881203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132327023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91239073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89325821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89893273</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224367</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90637603</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90637601</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224373</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119255844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,8 +2044,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89893274</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>